--- a/outputs/daily/predictions_2026-06-13.xlsx
+++ b/outputs/daily/predictions_2026-06-13.xlsx
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8365771526029933</v>
+        <v>0.8529532709971678</v>
       </c>
       <c r="L3" t="n">
-        <v>2.013072158218649</v>
+        <v>2.068196039824474</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06798318699770735</v>
+        <v>0.06773521793189932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1492550183707206</v>
+        <v>0.1537986887076337</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7827617946315721</v>
+        <v>0.778466093360467</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5653693960615428</v>
+        <v>0.5950764383808542</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6694777755179384</v>
+        <v>0.6992525362346195</v>
       </c>
       <c r="S3" t="n">
-        <v>2.280522224482062</v>
+        <v>2.380747463765381</v>
       </c>
       <c r="T3" t="n">
         <v>0.1723139167570108</v>
@@ -1156,58 +1156,58 @@
         <v>0.4532045241970775</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1373158460827138</v>
+        <v>0.1352869164017281</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2243763851881953</v>
+        <v>0.2190143218815901</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6383077687290911</v>
+        <v>0.6456987617166818</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5422926901364249</v>
+        <v>0.5589090797643568</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4577073098635751</v>
+        <v>0.4410909202356432</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5008405429914458</v>
+        <v>0.5108062563641846</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4991594570085542</v>
+        <v>0.4891937436358154</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.13652</v>
+        <v>0.135405</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.22435</v>
+        <v>0.218605</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.63913</v>
+        <v>0.64599</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.54111</v>
+        <v>0.5570850000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.50078</v>
+        <v>0.510105</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.836755</v>
+        <v>0.85343</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.014205</v>
+        <v>2.06655</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.85096</v>
+        <v>2.91998</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1218321071847152</v>
+        <v>0.1212256871381455</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2022682398065846</v>
+        <v>0.2027451921146985</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6758996530087004</v>
+        <v>0.676029120747156</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6758996530087004</v>
+        <v>0.676029120747156</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>14.70951928207961</v>
+        <v>14.76336875457307</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1218321071847152</v>
+        <v>0.1212256871381455</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05384892018700783</v>
+        <v>0.05349046920624623</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.7920917298099577</v>
+        <v>0.7896995217469485</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14.70951928207961</v>
+        <v>14.76336875457307</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1218321071847152</v>
+        <v>0.1212256871381455</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.05384892018700783</v>
+        <v>0.05349046920624623</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.7920917298099577</v>
+        <v>0.7896995217469485</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.117248028679922</v>
+        <v>0.115217723239233</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1071950886002771</v>
+        <v>0.1045383176677002</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1067416545831699</v>
+        <v>0.1019150871759742</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.09808702198136325</v>
+        <v>0.09827533391375014</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,23 +1292,23 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.0786762473805242</v>
+        <v>0.07943094630699128</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.06775088547094861</v>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BO3" t="n">
-        <v>0.06761012836939267</v>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
       <c r="BQ3" t="n">
-        <v>0.06581875101108764</v>
+        <v>0.0633758284317113</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,23 +1316,23 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04102868077823803</v>
+        <v>0.04191213376003604</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.04106969214790745</v>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BU3" t="n">
-        <v>0.04076225545192973</v>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0-4</t>
-        </is>
-      </c>
       <c r="BW3" t="n">
-        <v>0.03959524077871403</v>
+        <v>0.0405301363632754</v>
       </c>
     </row>
     <row r="4">
@@ -1385,31 +1385,31 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.553161397643803</v>
+        <v>1.531261346991902</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8941118471656182</v>
+        <v>0.8830118978175199</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5723044922211451</v>
+        <v>0.5597548283139765</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2514198450582821</v>
+        <v>0.2681330804481287</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1762756627205728</v>
+        <v>0.1721120912378949</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.461151438476042</v>
+        <v>0.4447232097088006</v>
       </c>
       <c r="R4" t="n">
-        <v>1.693283742856129</v>
+        <v>1.653465468943581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8267162571438706</v>
+        <v>0.8065345310564191</v>
       </c>
       <c r="T4" t="n">
         <v>0.4584917332356952</v>
@@ -1418,7 +1418,7 @@
         <v>0.3043678730466287</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2371403937176761</v>
+        <v>0.2371403937176762</v>
       </c>
       <c r="W4" t="n">
         <v>0.5230769675519009</v>
@@ -1427,58 +1427,58 @@
         <v>0.4541957023813316</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5157819567399647</v>
+        <v>0.51288696461773</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2794707806879252</v>
+        <v>0.2821054893208869</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2047472625721098</v>
+        <v>0.2050075460613831</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4425916932391429</v>
+        <v>0.434015532968582</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5574083067608571</v>
+        <v>0.565984467031418</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4779967332635722</v>
+        <v>0.4717263516920961</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5220032667364278</v>
+        <v>0.5282736483079039</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.515875</v>
+        <v>0.512375</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.278695</v>
+        <v>0.281155</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.20543</v>
+        <v>0.20647</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.44174</v>
+        <v>0.43344</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.47694</v>
+        <v>0.471885</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.553815</v>
+        <v>1.53136</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8939</v>
+        <v>0.885525</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.447715</v>
+        <v>2.416885</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5183393927059425</v>
+        <v>0.5125957791125164</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2769643887616142</v>
+        <v>0.2843083600757932</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2046962185324432</v>
+        <v>0.2030958608116904</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.5183393927059425</v>
+        <v>0.5125957791125164</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>5.672932863030398</v>
+        <v>5.810167041766929</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2046962185324432</v>
+        <v>0.2030958608116904</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.02842055581187042</v>
+        <v>0.03098376957379545</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1612279050507492</v>
+        <v>0.1800208768073672</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5.672932863030398</v>
+        <v>5.810167041766929</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2046962185324432</v>
+        <v>0.2030958608116904</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02842055581187042</v>
+        <v>0.03098376957379545</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1612279050507492</v>
+        <v>0.1800208768073672</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1321795268737097</v>
+        <v>0.1330158230119745</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.1223776107716765</v>
+        <v>0.1248519855528292</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.1043677331613627</v>
+        <v>0.1048487819823263</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.09854559671971691</v>
+        <v>0.1015247186884085</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.09331642668139434</v>
+        <v>0.09258272196206929</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>0.06535053025817329</v>
+        <v>0.06687750022175615</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>0.05403331143527251</v>
+        <v>0.05351696237623906</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.05371967315024091</v>
+        <v>0.05338843378071044</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.04831182389586663</v>
+        <v>0.04725611451327166</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04171766131549823</v>
+        <v>0.04087582251241929</v>
       </c>
     </row>
   </sheetData>
